--- a/data/people_of_intrest.xlsx
+++ b/data/people_of_intrest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kruppajo/work/GitHub/biodatascience/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jokruppa/GitHub/biodatascience/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA70823-AF47-414C-AC6E-A24DFC9E24D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4C40CE-6B85-EA4B-B036-A6200255ACBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15960" yWindow="2240" windowWidth="22440" windowHeight="17240" activeTab="3" xr2:uid="{78B40C30-F245-C14D-848B-8C574E4394BD}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="90">
   <si>
     <t>long</t>
   </si>
@@ -300,6 +300,15 @@
   </si>
   <si>
     <t>Positivism</t>
+  </si>
+  <si>
+    <t>Heinz von Foerster</t>
+  </si>
+  <si>
+    <t>Foerster</t>
+  </si>
+  <si>
+    <t>On Constructing a Reality</t>
   </si>
 </sst>
 </file>
@@ -1537,7 +1546,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2890218-D83F-DE44-8542-8FAE72B3846A}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
@@ -1797,6 +1806,26 @@
         <v>85</v>
       </c>
     </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13">
+        <v>1911</v>
+      </c>
+      <c r="D13">
+        <v>2002</v>
+      </c>
+      <c r="E13">
+        <v>1973</v>
+      </c>
+      <c r="F13" t="s">
+        <v>89</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H6" r:id="rId1" tooltip="Postskriptum" display="https://de.wikipedia.org/wiki/Postskriptum" xr:uid="{DFAE353B-04AB-6149-B8C7-09E056965AD3}"/>
